--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kalyana\Sprint 4 Email\Traveloka_DataAutomation_Performer_Email_S4\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A0036F-8094-4B1E-A4C2-845042678283}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41EB6B6-171A-4741-8093-5E8B6AD38798}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
   <si>
     <t>Name</t>
   </si>
@@ -165,9 +165,6 @@
     <t>RPA_Moon_SenderName</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_Email</t>
-  </si>
-  <si>
     <t>Traveloka_DataAutomation</t>
   </si>
   <si>
@@ -183,21 +180,18 @@
     <t>EmailRawFolderName</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_UploadBucket</t>
-  </si>
-  <si>
     <t>RPA_Moon_Email_Date</t>
   </si>
   <si>
     <t>Email_Raw_Data</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_PathMailTemplate</t>
-  </si>
-  <si>
     <t>ConverterPath</t>
   </si>
   <si>
+    <t>RPA_Moon_PathExcel</t>
+  </si>
+  <si>
     <t>RPA_Moon_AutoRetryMax</t>
   </si>
   <si>
@@ -210,7 +204,13 @@
     <t>AutoRetryPostpone</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_PathExcel</t>
+    <t>RPA_Moon_Cred_Gmail</t>
+  </si>
+  <si>
+    <t>RPA_Moon_UploadBucket</t>
+  </si>
+  <si>
+    <t>RPA_Moon_PathMailTemplate</t>
   </si>
   <si>
     <t>RPA_Moon_AutoRetryMaxDay</t>
@@ -225,31 +225,31 @@
     <t>AutoRetrySchedule</t>
   </si>
   <si>
+    <t>PathTabula</t>
+  </si>
+  <si>
+    <t>PathTemplateIata</t>
+  </si>
+  <si>
+    <t>Data\Template\Template_IATA.xlsx</t>
+  </si>
+  <si>
+    <t>RPA_Moon_PathTabula</t>
+  </si>
+  <si>
+    <t>SheetIdConfigChubb</t>
+  </si>
+  <si>
+    <t>RPA_Moon_SheetIdConfig_FS</t>
+  </si>
+  <si>
+    <t>RPA_Moon_Email_S4</t>
+  </si>
+  <si>
+    <t>RPA_Moon_PathSaKey</t>
+  </si>
+  <si>
     <t>PathSaKey</t>
-  </si>
-  <si>
-    <t>[Dev] RPA_Moon_PathSaKey</t>
-  </si>
-  <si>
-    <t>SheetIdConfigChubb</t>
-  </si>
-  <si>
-    <t>[Dev] RPA_Moon_SheetIdConfig_Transport</t>
-  </si>
-  <si>
-    <t>PathTemplateIata</t>
-  </si>
-  <si>
-    <t>Data\Template\Template_IATA.xlsx</t>
-  </si>
-  <si>
-    <t>[Dev] RPA_Moon_Cred_GmailCtrpa1</t>
-  </si>
-  <si>
-    <t>[Dev] RPA_Moon_PathTabula</t>
-  </si>
-  <si>
-    <t>PathTabula</t>
   </si>
 </sst>
 </file>
@@ -673,7 +673,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -694,7 +694,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>22</v>
@@ -702,42 +702,42 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1732,6 +1732,9 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <customProperties>
+    <customPr name="EpmWorksheetKeyString_GUID" r:id="rId2"/>
+  </customProperties>
 </worksheet>
 </file>
 
@@ -2890,12 +2893,15 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="EpmWorksheetKeyString_GUID" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z999"/>
+  <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
@@ -2945,7 +2951,7 @@
         <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
@@ -2958,26 +2964,26 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
@@ -3000,27 +3006,34 @@
       <c r="A9" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>67</v>
+      <c r="B9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4008,6 +4021,7 @@
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
     <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
